--- a/files/Meal Choice - All.xlsx
+++ b/files/Meal Choice - All.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb03e65629f95fa6/Documents/01 Personal/01 Web Development/01 Sites/11 C2C Rides/C2C_Rides/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="374" documentId="8_{D1BDAB1D-9912-46FA-B4D8-7D362212302F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5563BFA1-A148-414E-BC4C-F31DAE64AC92}"/>
+  <xr:revisionPtr revIDLastSave="382" documentId="8_{D1BDAB1D-9912-46FA-B4D8-7D362212302F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE4C0023-047F-4052-BFDC-416210F29BFA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{377EF423-DCCF-40A8-848B-6E396FEE9699}"/>
   </bookViews>
@@ -2945,8 +2945,8 @@
       <c r="P40" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="58" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -3594,8 +3594,8 @@
       <c r="P40" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="54" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="60" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -4304,8 +4304,8 @@
       <c r="Q40" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.11811023622047245" right="0.31496062992125984" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="55" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -4842,7 +4842,7 @@
       <c r="O17" s="7"/>
       <c r="P17" s="9"/>
     </row>
-    <row r="18" spans="2:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B18" s="15" t="s">
         <v>15</v>
       </c>
@@ -5056,8 +5056,8 @@
       <c r="Q40" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="42" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="47" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
